--- a/artfynd/A 37401-2024 artfynd.xlsx
+++ b/artfynd/A 37401-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105383</v>
+        <v>120101890</v>
       </c>
       <c r="B2" t="n">
-        <v>90776</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmården, Srm</t>
+          <t>Kolmården, Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581696</v>
+        <v>581691</v>
       </c>
       <c r="R2" t="n">
-        <v>6508913</v>
+        <v>6508906</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101890</v>
+        <v>120105383</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>90776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,40 +806,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmården, Kolmården, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581691</v>
+        <v>581696</v>
       </c>
       <c r="R3" t="n">
-        <v>6508906</v>
+        <v>6508913</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37401-2024 artfynd.xlsx
+++ b/artfynd/A 37401-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101890</v>
+        <v>120105383</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>90794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmården, Kolmården, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581691</v>
+        <v>581696</v>
       </c>
       <c r="R2" t="n">
-        <v>6508906</v>
+        <v>6508913</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105383</v>
+        <v>120101890</v>
       </c>
       <c r="B3" t="n">
-        <v>90776</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,44 +810,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmården, Srm</t>
+          <t>Kolmården, Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581696</v>
+        <v>581691</v>
       </c>
       <c r="R3" t="n">
-        <v>6508913</v>
+        <v>6508906</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37401-2024 artfynd.xlsx
+++ b/artfynd/A 37401-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105383</v>
+        <v>120101890</v>
       </c>
       <c r="B2" t="n">
-        <v>90794</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmården, Srm</t>
+          <t>Kolmården, Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581696</v>
+        <v>581691</v>
       </c>
       <c r="R2" t="n">
-        <v>6508913</v>
+        <v>6508906</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101890</v>
+        <v>120105383</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>90794</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,40 +806,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmården, Kolmården, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581691</v>
+        <v>581696</v>
       </c>
       <c r="R3" t="n">
-        <v>6508906</v>
+        <v>6508913</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37401-2024 artfynd.xlsx
+++ b/artfynd/A 37401-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101890</v>
+        <v>120105383</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>90794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmården, Kolmården, Srm</t>
+          <t>Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581691</v>
+        <v>581696</v>
       </c>
       <c r="R2" t="n">
-        <v>6508906</v>
+        <v>6508913</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105383</v>
+        <v>120101890</v>
       </c>
       <c r="B3" t="n">
-        <v>90794</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,44 +810,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmården, Srm</t>
+          <t>Kolmården, Kolmården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581696</v>
+        <v>581691</v>
       </c>
       <c r="R3" t="n">
-        <v>6508913</v>
+        <v>6508906</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
